--- a/indicator-performance-table.xlsx
+++ b/indicator-performance-table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="230">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -690,6 +690,18 @@
   </si>
   <si>
     <t xml:space="preserve">Over the last ten years, the proportion of individuals in households spending 30% or more of household income on housing costs generally decreased slowly from a high of 11% in 2013/14 to a low of 6% in 2021/22. However, there has consistently been a larger proportion spending 30% or more of household income on housing costs in the rental sectors compared to the overall population. Changes are being made to the way poverty and income statistics are produced in Northern Ireland to improve the quality, coherence and completeness of income-based poverty statistics. Consequently, the figures for this indicator are under review. The latest information and revised statistics are available &lt;a href = 'https://www.communities-ni.gov.uk/topics/family-resources-survey-and-poverty-analysis' target = '_blank'&gt;from this link. &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There were a number of significant changes to the survey methodology from 2020, due to the Covid-19 pandemic. In addition to these changes, the impact of the pandemic and the resultant introduction of new public health regulations, guidance and advice may have also fundamentally changed peoples’ behaviour and attitudes.  While 2020 to 2024 results can be compared to each other, care should be taken in reaching any conclusions based on these data and comparisons to previous years. The base year for this indicator has been set to 2022.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economic activity has increased gradually in recent years. Economic activity post-pandemic has recovered substantially and the latest 2026 data is now at a series high. Over the second quarter of 2026, economic output in Northern Ireland increased by 1.0%, mainly driven by increased activity in the Production and Services sectors. Quarterly figures are available &lt;a href = 'https://www.nisra.gov.uk/statistics/economic-output-statistics/ni-composite-economic-index' target = '_blank'&gt;from this link. &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Court disruptions, as a result of the Covid-19 pandemic, led to delays and resulted in a backlog of cases to be cleared in 2021/22 and subsequent years. The figure for 2025/26 (209 days) is 17 days less than the figure for 2021/22 (226 days).</t>
   </si>
 </sst>
 </file>
@@ -749,8 +761,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:J417" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:J417"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:J469" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:J469"/>
   <tableColumns count="10">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="domain"/>
@@ -14338,6 +14350,1666 @@
         <v>217</v>
       </c>
     </row>
+    <row r="418">
+      <c r="A418" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B418" t="s">
+        <v>10</v>
+      </c>
+      <c r="C418" t="s">
+        <v>11</v>
+      </c>
+      <c r="D418" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E418" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="F418" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G418" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H418" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="I418" t="s">
+        <v>15</v>
+      </c>
+      <c r="J418" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B419" t="s">
+        <v>10</v>
+      </c>
+      <c r="C419" t="s">
+        <v>17</v>
+      </c>
+      <c r="D419" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E419" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F419" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G419" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H419" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I419" t="s">
+        <v>21</v>
+      </c>
+      <c r="J419" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B420" t="s">
+        <v>10</v>
+      </c>
+      <c r="C420" t="s">
+        <v>23</v>
+      </c>
+      <c r="D420" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E420" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F420" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G420" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H420" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="I420" t="s">
+        <v>21</v>
+      </c>
+      <c r="J420" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B421" t="s">
+        <v>10</v>
+      </c>
+      <c r="C421" t="s">
+        <v>26</v>
+      </c>
+      <c r="D421" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E421" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F421" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G421" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H421" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I421" t="s">
+        <v>30</v>
+      </c>
+      <c r="J421" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B422" t="s">
+        <v>32</v>
+      </c>
+      <c r="C422" t="s">
+        <v>33</v>
+      </c>
+      <c r="D422" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E422" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F422" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G422" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H422" s="3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="I422" t="s">
+        <v>15</v>
+      </c>
+      <c r="J422" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B423" t="s">
+        <v>32</v>
+      </c>
+      <c r="C423" t="s">
+        <v>37</v>
+      </c>
+      <c r="D423" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E423" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F423" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G423" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H423" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I423" t="s">
+        <v>21</v>
+      </c>
+      <c r="J423" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B424" t="s">
+        <v>32</v>
+      </c>
+      <c r="C424" t="s">
+        <v>39</v>
+      </c>
+      <c r="D424" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E424" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F424" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G424" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H424" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="I424" t="s">
+        <v>21</v>
+      </c>
+      <c r="J424" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B425" t="s">
+        <v>32</v>
+      </c>
+      <c r="C425" t="s">
+        <v>44</v>
+      </c>
+      <c r="D425" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E425" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F425" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G425" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H425" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I425" t="s">
+        <v>15</v>
+      </c>
+      <c r="J425" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B426" t="s">
+        <v>32</v>
+      </c>
+      <c r="C426" t="s">
+        <v>47</v>
+      </c>
+      <c r="D426" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E426" s="3" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="F426" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G426" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H426" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="I426" t="s">
+        <v>21</v>
+      </c>
+      <c r="J426" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B427" t="s">
+        <v>32</v>
+      </c>
+      <c r="C427" t="s">
+        <v>50</v>
+      </c>
+      <c r="D427" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E427" s="3" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="F427" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G427" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H427" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="I427" t="s">
+        <v>30</v>
+      </c>
+      <c r="J427" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B428" t="s">
+        <v>32</v>
+      </c>
+      <c r="C428" t="s">
+        <v>53</v>
+      </c>
+      <c r="D428" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E428" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F428" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G428" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H428" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="I428" t="s">
+        <v>15</v>
+      </c>
+      <c r="J428" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B429" t="s">
+        <v>32</v>
+      </c>
+      <c r="C429" t="s">
+        <v>56</v>
+      </c>
+      <c r="D429" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E429" s="3" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="F429" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G429" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H429" s="3" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="I429" t="s">
+        <v>30</v>
+      </c>
+      <c r="J429" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B430" t="s">
+        <v>32</v>
+      </c>
+      <c r="C430" t="s">
+        <v>59</v>
+      </c>
+      <c r="D430" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E430" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F430" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G430" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H430" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I430" t="s">
+        <v>30</v>
+      </c>
+      <c r="J430" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B431" t="s">
+        <v>63</v>
+      </c>
+      <c r="C431" t="s">
+        <v>64</v>
+      </c>
+      <c r="D431" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E431" s="3" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="F431" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G431" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H431" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I431" t="s">
+        <v>15</v>
+      </c>
+      <c r="J431" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B432" t="s">
+        <v>63</v>
+      </c>
+      <c r="C432" t="s">
+        <v>67</v>
+      </c>
+      <c r="D432" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E432" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F432" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G432" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H432" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I432" t="s">
+        <v>30</v>
+      </c>
+      <c r="J432" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B433" t="s">
+        <v>63</v>
+      </c>
+      <c r="C433" t="s">
+        <v>71</v>
+      </c>
+      <c r="D433" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E433" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F433" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G433" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H433" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I433" t="s">
+        <v>30</v>
+      </c>
+      <c r="J433" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B434" t="s">
+        <v>63</v>
+      </c>
+      <c r="C434" t="s">
+        <v>73</v>
+      </c>
+      <c r="D434" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E434" s="3" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F434" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G434" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H434" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I434" t="s">
+        <v>21</v>
+      </c>
+      <c r="J434" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B435" t="s">
+        <v>75</v>
+      </c>
+      <c r="C435" t="s">
+        <v>76</v>
+      </c>
+      <c r="D435" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E435" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="F435" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G435" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H435" s="3" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="I435" t="s">
+        <v>30</v>
+      </c>
+      <c r="J435" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B436" t="s">
+        <v>75</v>
+      </c>
+      <c r="C436" t="s">
+        <v>78</v>
+      </c>
+      <c r="D436" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E436" s="3" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="F436" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G436" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H436" s="3" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="I436" t="s">
+        <v>21</v>
+      </c>
+      <c r="J436" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B437" t="s">
+        <v>75</v>
+      </c>
+      <c r="C437" t="s">
+        <v>83</v>
+      </c>
+      <c r="D437" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E437" s="3" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="F437" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G437" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H437" s="3" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="I437" t="s">
+        <v>30</v>
+      </c>
+      <c r="J437" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B438" t="s">
+        <v>75</v>
+      </c>
+      <c r="C438" t="s">
+        <v>86</v>
+      </c>
+      <c r="D438" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E438" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F438" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G438" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H438" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="I438" t="s">
+        <v>15</v>
+      </c>
+      <c r="J438" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B439" t="s">
+        <v>75</v>
+      </c>
+      <c r="C439" t="s">
+        <v>89</v>
+      </c>
+      <c r="D439" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E439" s="3" t="n">
+        <v>173</v>
+      </c>
+      <c r="F439" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G439" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H439" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="I439" t="s">
+        <v>21</v>
+      </c>
+      <c r="J439" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B440" t="s">
+        <v>75</v>
+      </c>
+      <c r="C440" t="s">
+        <v>94</v>
+      </c>
+      <c r="D440" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E440" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F440" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G440" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H440" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="I440" t="s">
+        <v>21</v>
+      </c>
+      <c r="J440" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B441" t="s">
+        <v>98</v>
+      </c>
+      <c r="C441" t="s">
+        <v>99</v>
+      </c>
+      <c r="D441" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E441" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="F441" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G441" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H441" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I441" t="s">
+        <v>15</v>
+      </c>
+      <c r="J441" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B442" t="s">
+        <v>98</v>
+      </c>
+      <c r="C442" t="s">
+        <v>101</v>
+      </c>
+      <c r="D442" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E442" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F442" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G442" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H442" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I442" t="s">
+        <v>30</v>
+      </c>
+      <c r="J442" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B443" t="s">
+        <v>98</v>
+      </c>
+      <c r="C443" t="s">
+        <v>104</v>
+      </c>
+      <c r="D443" s="3"/>
+      <c r="E443" s="3"/>
+      <c r="F443" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G443" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H443" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="I443" t="s">
+        <v>61</v>
+      </c>
+      <c r="J443" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B444" t="s">
+        <v>98</v>
+      </c>
+      <c r="C444" t="s">
+        <v>106</v>
+      </c>
+      <c r="D444" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E444" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F444" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G444" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H444" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I444" t="s">
+        <v>21</v>
+      </c>
+      <c r="J444" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B445" t="s">
+        <v>108</v>
+      </c>
+      <c r="C445" t="s">
+        <v>109</v>
+      </c>
+      <c r="D445" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E445" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F445" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G445" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H445" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I445" t="s">
+        <v>15</v>
+      </c>
+      <c r="J445" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B446" t="s">
+        <v>108</v>
+      </c>
+      <c r="C446" t="s">
+        <v>111</v>
+      </c>
+      <c r="D446" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E446" s="3" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="F446" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G446" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H446" s="3" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="I446" t="s">
+        <v>15</v>
+      </c>
+      <c r="J446" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B447" t="s">
+        <v>108</v>
+      </c>
+      <c r="C447" t="s">
+        <v>114</v>
+      </c>
+      <c r="D447" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E447" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F447" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G447" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H447" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I447" t="s">
+        <v>15</v>
+      </c>
+      <c r="J447" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B448" t="s">
+        <v>108</v>
+      </c>
+      <c r="C448" t="s">
+        <v>117</v>
+      </c>
+      <c r="D448" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E448" s="3" t="n">
+        <v>66.9</v>
+      </c>
+      <c r="F448" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G448" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H448" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="I448" t="s">
+        <v>15</v>
+      </c>
+      <c r="J448" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B449" t="s">
+        <v>108</v>
+      </c>
+      <c r="C449" t="s">
+        <v>119</v>
+      </c>
+      <c r="D449" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E449" s="3" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="F449" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G449" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H449" s="3" t="n">
+        <v>62.21</v>
+      </c>
+      <c r="I449" t="s">
+        <v>30</v>
+      </c>
+      <c r="J449" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B450" t="s">
+        <v>108</v>
+      </c>
+      <c r="C450" t="s">
+        <v>121</v>
+      </c>
+      <c r="D450" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E450" s="3" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F450" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G450" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H450" s="3" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="I450" t="s">
+        <v>15</v>
+      </c>
+      <c r="J450" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B451" t="s">
+        <v>108</v>
+      </c>
+      <c r="C451" t="s">
+        <v>123</v>
+      </c>
+      <c r="D451" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E451" s="3" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="F451" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G451" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H451" s="3" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="I451" t="s">
+        <v>15</v>
+      </c>
+      <c r="J451" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B452" t="s">
+        <v>108</v>
+      </c>
+      <c r="C452" t="s">
+        <v>126</v>
+      </c>
+      <c r="D452" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E452" s="3" t="n">
+        <v>1170.4</v>
+      </c>
+      <c r="F452" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G452" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H452" s="3" t="n">
+        <v>1000.7</v>
+      </c>
+      <c r="I452" t="s">
+        <v>21</v>
+      </c>
+      <c r="J452" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B453" t="s">
+        <v>108</v>
+      </c>
+      <c r="C453" t="s">
+        <v>128</v>
+      </c>
+      <c r="D453" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E453" s="3" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="F453" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G453" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H453" s="3" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="I453" t="s">
+        <v>15</v>
+      </c>
+      <c r="J453" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B454" t="s">
+        <v>131</v>
+      </c>
+      <c r="C454" t="s">
+        <v>132</v>
+      </c>
+      <c r="D454" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E454" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F454" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G454" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H454" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I454" t="s">
+        <v>30</v>
+      </c>
+      <c r="J454" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B455" t="s">
+        <v>131</v>
+      </c>
+      <c r="C455" t="s">
+        <v>134</v>
+      </c>
+      <c r="D455" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E455" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F455" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G455" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H455" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I455" t="s">
+        <v>30</v>
+      </c>
+      <c r="J455" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B456" t="s">
+        <v>131</v>
+      </c>
+      <c r="C456" t="s">
+        <v>136</v>
+      </c>
+      <c r="D456" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E456" s="3" t="n">
+        <v>226</v>
+      </c>
+      <c r="F456" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G456" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H456" s="3" t="n">
+        <v>209</v>
+      </c>
+      <c r="I456" t="s">
+        <v>15</v>
+      </c>
+      <c r="J456" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B457" t="s">
+        <v>131</v>
+      </c>
+      <c r="C457" t="s">
+        <v>140</v>
+      </c>
+      <c r="D457" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E457" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F457" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G457" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H457" s="3" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="I457" t="s">
+        <v>21</v>
+      </c>
+      <c r="J457" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B458" t="s">
+        <v>131</v>
+      </c>
+      <c r="C458" t="s">
+        <v>142</v>
+      </c>
+      <c r="D458" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E458" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F458" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G458" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H458" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I458" t="s">
+        <v>30</v>
+      </c>
+      <c r="J458" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B459" t="s">
+        <v>145</v>
+      </c>
+      <c r="C459" t="s">
+        <v>146</v>
+      </c>
+      <c r="D459" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E459" s="3" t="n">
+        <v>68.4</v>
+      </c>
+      <c r="F459" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G459" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H459" s="3" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="I459" t="s">
+        <v>30</v>
+      </c>
+      <c r="J459" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B460" t="s">
+        <v>145</v>
+      </c>
+      <c r="C460" t="s">
+        <v>148</v>
+      </c>
+      <c r="D460" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E460" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F460" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G460" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H460" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I460" t="s">
+        <v>15</v>
+      </c>
+      <c r="J460" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B461" t="s">
+        <v>145</v>
+      </c>
+      <c r="C461" t="s">
+        <v>150</v>
+      </c>
+      <c r="D461" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E461" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F461" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G461" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H461" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="I461" t="s">
+        <v>30</v>
+      </c>
+      <c r="J461" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B462" t="s">
+        <v>152</v>
+      </c>
+      <c r="C462" t="s">
+        <v>153</v>
+      </c>
+      <c r="D462" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E462" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F462" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G462" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H462" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="I462" t="s">
+        <v>30</v>
+      </c>
+      <c r="J462" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B463" t="s">
+        <v>152</v>
+      </c>
+      <c r="C463" t="s">
+        <v>154</v>
+      </c>
+      <c r="D463" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E463" s="3" t="n">
+        <v>10135</v>
+      </c>
+      <c r="F463" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G463" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H463" s="3" t="n">
+        <v>10852</v>
+      </c>
+      <c r="I463" t="s">
+        <v>21</v>
+      </c>
+      <c r="J463" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B464" t="s">
+        <v>152</v>
+      </c>
+      <c r="C464" t="s">
+        <v>156</v>
+      </c>
+      <c r="D464" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E464" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F464" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G464" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H464" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I464" t="s">
+        <v>30</v>
+      </c>
+      <c r="J464" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B465" t="s">
+        <v>152</v>
+      </c>
+      <c r="C465" t="s">
+        <v>159</v>
+      </c>
+      <c r="D465" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E465" s="3" t="n">
+        <v>31407</v>
+      </c>
+      <c r="F465" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G465" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H465" s="3" t="n">
+        <v>39008</v>
+      </c>
+      <c r="I465" t="s">
+        <v>21</v>
+      </c>
+      <c r="J465" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B466" t="s">
+        <v>161</v>
+      </c>
+      <c r="C466" t="s">
+        <v>162</v>
+      </c>
+      <c r="D466" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E466" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F466" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G466" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H466" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I466" t="s">
+        <v>15</v>
+      </c>
+      <c r="J466" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B467" t="s">
+        <v>161</v>
+      </c>
+      <c r="C467" t="s">
+        <v>164</v>
+      </c>
+      <c r="D467" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E467" s="3" t="n">
+        <v>78.6</v>
+      </c>
+      <c r="F467" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G467" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H467" s="3" t="n">
+        <v>76.1</v>
+      </c>
+      <c r="I467" t="s">
+        <v>21</v>
+      </c>
+      <c r="J467" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B468" t="s">
+        <v>161</v>
+      </c>
+      <c r="C468" t="s">
+        <v>165</v>
+      </c>
+      <c r="D468" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E468" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F468" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G468" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H468" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="I468" t="s">
+        <v>30</v>
+      </c>
+      <c r="J468" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B469" t="s">
+        <v>161</v>
+      </c>
+      <c r="C469" t="s">
+        <v>168</v>
+      </c>
+      <c r="D469" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E469" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="F469" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G469" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H469" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="I469" t="s">
+        <v>30</v>
+      </c>
+      <c r="J469" t="s">
+        <v>217</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
